--- a/data/trans_bre/IP07B_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP07B_R-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,297 +619,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10,63</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,35</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,37%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>10.63481736557168</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1.46121918992218</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6.348642135038018</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>4.003149764207448</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1536844619501508</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.0205604477245077</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.07975875374738484</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.06858544367738476</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1,62; 19,69</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,04; 10,56</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-0,36; 13,34</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-10,21; 16,84</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2,6; 30,61</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-9,6; 16,02</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 17,88</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-15,21; 33,58</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.624471191798257</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.041317934809427</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.3633209860700146</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-10.20541335088977</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.02602589049379824</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.09598430975355898</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.003766112965595343</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.1521291971740312</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>19.68596814762318</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>10.56265857851993</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>13.34426328156966</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>16.84384154801629</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.3061280634631196</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1602304425052849</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.1787693168886965</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.3357583376381474</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>12-15</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,93</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-3,92%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-4,18%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,44%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14,1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-10,69; 3,99</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-11,57; 4,99</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 4,96</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,87; 21,51</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-13,14; 5,27</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-14,98; 7,07</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-10,51; 6,18</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 40,67</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.098628047104579</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.071188333714281</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.927352772035685</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>8.700147535069069</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.03920955970070571</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.04182948424828906</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.0344389621788771</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.1410453711438785</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,98</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>11,54%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-10.69244261194427</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-11.57192568558868</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-9.147745662283199</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-2.868831373954359</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1314093351974183</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1497999616918891</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1051184657755683</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.0415751529489559</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3,29; 7,84</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,89; 5,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,63; 6,44</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 16,11</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-4,13; 10,75</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 7,39</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 8,13</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-2,17; 29,83</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.994828688650891</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.985067790230633</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.96137997268735</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>21.51289969818313</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.05273829454170128</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.07069094146781052</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.06176914869027827</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4066717597332506</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>2.33469743258008</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.9148064283611035</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.846761306379352</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.977610046085503</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.03109063332127218</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.01265204131418883</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.02244353353207117</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.1153746121960451</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-3.288548727368842</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.890190382440007</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.63181690645994</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.391655288408511</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.04126254752211242</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.09151345240261692</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.04407075446241911</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.02166209500842432</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.838969169407325</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.144292900070104</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.442120832788077</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>16.10560359550835</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1075143071863551</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.07391672575594196</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.08127743754118168</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2982686769489881</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -908,11 +917,11 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A1:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
